--- a/Autoencoder_Experiment_Results.xlsx
+++ b/Autoencoder_Experiment_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brayan Gutierrez\Desktop\RNAseq-AMD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761C0E98-DBC8-4B7F-82E0-9CA896CED8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364B190A-9BC1-49A4-AF93-975CD3D0A2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63232B45-B086-4A96-A27B-BB842C853CB4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="17">
   <si>
     <t>Latent Components</t>
   </si>
@@ -85,12 +85,18 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>615 Feature Metasheet</t>
+  </si>
+  <si>
+    <t>17 Feature Metasheet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +114,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -151,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -294,11 +308,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -355,6 +406,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -691,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906D079D-78EA-444A-A005-F7BBAB2E853D}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" style="1" customWidth="1"/>
@@ -703,82 +763,64 @@
     <col min="9" max="10" width="23.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.79</v>
-      </c>
-      <c r="D2" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0.70150000000000001</v>
-      </c>
-      <c r="J2" s="10">
-        <v>0.77390000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="D3" s="10">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>14</v>
@@ -793,334 +835,802 @@
         <v>14</v>
       </c>
       <c r="I3" s="9">
-        <v>0.71120000000000005</v>
+        <v>0.70150000000000001</v>
       </c>
       <c r="J3" s="10">
-        <v>0.78859999999999997</v>
+        <v>0.77390000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D4" s="10">
         <v>0.76</v>
       </c>
-      <c r="D4" s="10">
+      <c r="E4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.71120000000000005</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0.78859999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="D5" s="10">
         <v>0.6</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="E5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="9">
         <v>0.50780000000000003</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J5" s="10">
         <v>0.56910000000000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.79</v>
-      </c>
-      <c r="D5" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="E5" s="11">
-        <v>0.78900000000000003</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="H5" s="12">
-        <v>0.23</v>
-      </c>
-      <c r="I5" s="11">
-        <v>0.73399999999999999</v>
-      </c>
-      <c r="J5" s="12">
-        <v>0.79020000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="3">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="D6" s="12">
         <v>0.75</v>
       </c>
       <c r="E6" s="11">
-        <v>0.68700000000000006</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="F6" s="3">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="G6" s="3">
-        <v>0.10199999999999999</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="H6" s="12">
-        <v>9.5000000000000001E-2</v>
+        <v>0.23</v>
       </c>
       <c r="I6" s="11">
-        <v>0.75439999999999996</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="J6" s="12">
-        <v>0.80869999999999997</v>
+        <v>0.79020000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H7" s="12">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.75439999999999996</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0.80869999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3">
         <v>0.79</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D8" s="12">
         <v>0.76</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E8" s="11">
         <v>0.77100000000000002</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F8" s="3">
         <v>0.28299999999999997</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G8" s="3">
         <v>0.192</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H8" s="12">
         <v>0.188</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I8" s="11">
         <v>0.63149999999999995</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J8" s="12">
         <v>0.66539999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.76</v>
-      </c>
-      <c r="D8" s="14">
-        <v>0.7</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0.156</v>
-      </c>
-      <c r="G8" s="4">
-        <v>9.4E-2</v>
-      </c>
-      <c r="H8" s="14">
-        <v>0.09</v>
-      </c>
-      <c r="I8" s="13">
-        <v>0.72219999999999995</v>
-      </c>
-      <c r="J8" s="14">
-        <v>0.77490000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="4">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="D9" s="14">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="13">
-        <v>0.53</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="F9" s="4">
-        <v>3.0000000000000001E-3</v>
+        <v>0.156</v>
       </c>
       <c r="G9" s="4">
-        <v>7.0000000000000001E-3</v>
+        <v>9.4E-2</v>
       </c>
       <c r="H9" s="14">
-        <v>2E-3</v>
+        <v>0.09</v>
       </c>
       <c r="I9" s="13">
-        <v>0.7077</v>
+        <v>0.72219999999999995</v>
       </c>
       <c r="J9" s="14">
-        <v>0.74299999999999999</v>
+        <v>0.77490000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0.69</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0.53</v>
+      </c>
+      <c r="F10" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>2E-3</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0.7077</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0.74299999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4">
         <v>0.75</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D11" s="14">
         <v>0.7</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E11" s="13">
         <v>0.56599999999999995</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F11" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G11" s="4">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H11" s="14">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I11" s="13">
         <v>0.61550000000000005</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J11" s="14">
         <v>0.68669999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
-        <v>16</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.69</v>
-      </c>
-      <c r="E11" s="15">
-        <v>0.72299999999999998</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.113</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.109</v>
-      </c>
-      <c r="I11" s="15">
-        <v>0.52980000000000005</v>
-      </c>
-      <c r="J11" s="16">
-        <v>0.63829999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0.69</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.113</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0.109</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0.52980000000000005</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0.63829999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5">
         <v>0.64</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D13" s="16">
         <v>0.53</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E13" s="15">
         <v>0.66300000000000003</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="5">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G13" s="5">
         <v>7.8E-2</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H13" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I13" s="15">
         <v>0.58169999999999999</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J13" s="16">
         <v>0.65700000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
         <v>4</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B14" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C14" s="18">
         <v>0.65</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D14" s="19">
         <v>0.54</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E14" s="17">
         <v>0.62</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F14" s="18">
         <v>0.05</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G14" s="18">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H14" s="19">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I14" s="17">
         <v>0.43930000000000002</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J14" s="19">
         <v>0.53490000000000004</v>
       </c>
     </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="J18" s="10">
+        <v>0.76900000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.76</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="J19" s="10">
+        <v>0.81599999999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0.61</v>
+      </c>
+      <c r="J20" s="10">
+        <v>0.66800000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="J21" s="12">
+        <v>0.751</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="D22" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H22" s="12">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="D23" s="12">
+        <v>0.76</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H23" s="12">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="I23" s="11">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="J23" s="12">
+        <v>0.72899999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
+        <v>16</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="D24" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="F24" s="4">
+        <v>7.8E-2</v>
+      </c>
+      <c r="G24" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="H24" s="14">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0.62</v>
+      </c>
+      <c r="J24" s="14">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>8</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="D25" s="14">
+        <v>0.69</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="F25" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="H25" s="14">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="J25" s="14">
+        <v>0.626</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>4</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D26" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F26" s="4">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H26" s="14">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="J26" s="14">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
+        <v>16</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="D27" s="16">
+        <v>0.69</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0.126</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0.122</v>
+      </c>
+      <c r="H27" s="16">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="J27" s="16">
+        <v>0.70699999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>8</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="D28" s="16">
+        <v>0.53</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0.59</v>
+      </c>
+      <c r="F28" s="5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="H28" s="16">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J28" s="16">
+        <v>0.60199999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17">
+        <v>4</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="D29" s="19">
+        <v>0.54</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="F29" s="18">
+        <v>0.11</v>
+      </c>
+      <c r="G29" s="18">
+        <v>0.156</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="J29" s="19">
+        <v>0.59</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A16:J16"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Autoencoder_Experiment_Results.xlsx
+++ b/Autoencoder_Experiment_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brayan Gutierrez\Desktop\RNAseq-AMD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364B190A-9BC1-49A4-AF93-975CD3D0A2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD640FF2-7FBC-47CC-9F80-1C66FBBA30E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63232B45-B086-4A96-A27B-BB842C853CB4}"/>
   </bookViews>
@@ -86,10 +86,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>615 Feature Metasheet</t>
+    <t>17 Feature Metasheet</t>
   </si>
   <si>
-    <t>17 Feature Metasheet</t>
+    <t>613 Feature Metasheet</t>
   </si>
 </sst>
 </file>
@@ -765,7 +765,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1196,7 +1196,7 @@
     <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -1248,10 +1248,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>0.79</v>
+        <v>0.69</v>
       </c>
       <c r="D18" s="10">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>14</v>
@@ -1280,10 +1280,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="2">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="D19" s="10">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>14</v>
@@ -1312,10 +1312,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="2">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="D20" s="10">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>14</v>
@@ -1344,7 +1344,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="3">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="D21" s="12">
         <v>0.75</v>
@@ -1376,10 +1376,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="3">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="D22" s="12">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="11">
         <v>0.68700000000000006</v>
@@ -1408,10 +1408,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="3">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="D23" s="12">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="E23" s="11">
         <v>0.68700000000000006</v>
@@ -1440,10 +1440,10 @@
         <v>3</v>
       </c>
       <c r="C24" s="4">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="14">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="E24" s="13">
         <v>0.64500000000000002</v>
@@ -1472,10 +1472,10 @@
         <v>3</v>
       </c>
       <c r="C25" s="4">
-        <v>0.72</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D25" s="14">
-        <v>0.69</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13">
         <v>0.54800000000000004</v>
@@ -1504,10 +1504,10 @@
         <v>3</v>
       </c>
       <c r="C26" s="4">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="D26" s="14">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="13">
         <v>0.56000000000000005</v>
@@ -1536,10 +1536,10 @@
         <v>4</v>
       </c>
       <c r="C27" s="5">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="D27" s="16">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
       <c r="E27" s="15">
         <v>0.70499999999999996</v>
@@ -1568,10 +1568,10 @@
         <v>4</v>
       </c>
       <c r="C28" s="5">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="D28" s="16">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="E28" s="15">
         <v>0.59</v>
@@ -1600,10 +1600,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="18">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="D29" s="19">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="E29" s="17">
         <v>0.69899999999999995</v>
